--- a/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt1_rubricas.xlsx
@@ -1800,13 +1800,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0F9886A-AFB5-4B7E-BDD8-31232F54412F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683E9982-42D4-44E9-BA5E-64AC9B903392}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BCB4B8-B7E7-497A-BC92-96D876F2AF6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A38CCCD2-8C91-482C-80DF-9C62BB7AB610}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F7769FA-8BDD-4D77-9269-2CB44941001D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F53634CD-925E-4876-AF48-76396A548EC5}"/>
 </file>